--- a/templates/library_import_templates.xlsx
+++ b/templates/library_import_templates.xlsx
@@ -17957,7 +17957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -18413,6 +18413,27 @@
       <c r="D21" t="inlineStr">
         <is>
           <t>Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BOOK BULK IMPORT NOTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>For bulk adding books, CSV files are recommended because they are easier to prepare, edit, and import.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Use the book_import_template.csv file for the fastest and most reliable book importing process.</t>
         </is>
       </c>
     </row>
